--- a/input/ES/alignment_targets_employment.xlsx
+++ b/input/ES/alignment_targets_employment.xlsx
@@ -103,7 +103,7 @@
     <t>Produced</t>
   </si>
   <si>
-    <t>11 Aug 2026</t>
+    <t>26 Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -2897,7 +2897,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="14">
-        <v>0.70199390227450553</v>
+        <v>0.70130623386525604</v>
       </c>
     </row>
     <row r="3">
@@ -2905,7 +2905,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="15">
-        <v>0.67271556420263046</v>
+        <v>0.67112979201428136</v>
       </c>
     </row>
     <row r="4">
@@ -2913,7 +2913,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="16">
-        <v>0.67589171295268846</v>
+        <v>0.67388943194244355</v>
       </c>
     </row>
     <row r="5">
@@ -2921,7 +2921,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="17">
-        <v>0.69332750680608857</v>
+        <v>0.69081583133495783</v>
       </c>
     </row>
     <row r="6">
@@ -2929,7 +2929,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="18">
-        <v>0.73474452646157151</v>
+        <v>0.73304370218404258</v>
       </c>
     </row>
     <row r="7">
@@ -2937,7 +2937,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="19">
-        <v>0.74710399707034547</v>
+        <v>0.74603176394214099</v>
       </c>
     </row>
     <row r="8">
@@ -2945,7 +2945,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="20">
-        <v>0.76376489266255066</v>
+        <v>0.76213531773424492</v>
       </c>
     </row>
     <row r="9">
@@ -2953,7 +2953,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="21">
-        <v>0.77191979701418712</v>
+        <v>0.77017750255819073</v>
       </c>
     </row>
     <row r="10">
@@ -2961,7 +2961,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="22">
-        <v>0.77940846722142298</v>
+        <v>0.77819871223912374</v>
       </c>
     </row>
     <row r="11">
@@ -2969,7 +2969,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="23">
-        <v>0.80421608998331973</v>
+        <v>0.80269783330950806</v>
       </c>
     </row>
     <row r="12">
@@ -2977,7 +2977,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="24">
-        <v>0.78943082405591014</v>
+        <v>0.7886052660937054</v>
       </c>
     </row>
     <row r="13">
@@ -2985,7 +2985,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="25">
-        <v>0.80811991390140625</v>
+        <v>0.80759932126814915</v>
       </c>
     </row>
     <row r="14">
@@ -2993,7 +2993,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="26">
-        <v>0.80854027984617205</v>
+        <v>0.80806859574553347</v>
       </c>
     </row>
   </sheetData>
@@ -3018,7 +3018,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="40">
-        <v>0.3621240098912531</v>
+        <v>0.36124158721256311</v>
       </c>
     </row>
     <row r="3">
@@ -3026,7 +3026,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="41">
-        <v>0.29513758396842316</v>
+        <v>0.29461384895205362</v>
       </c>
     </row>
     <row r="4">
@@ -3034,7 +3034,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="42">
-        <v>0.30973069013185051</v>
+        <v>0.30749925807673023</v>
       </c>
     </row>
     <row r="5">
@@ -3042,7 +3042,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="43">
-        <v>0.29257778069218049</v>
+        <v>0.29072037370196496</v>
       </c>
     </row>
     <row r="6">
@@ -3050,7 +3050,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="44">
-        <v>0.30012459579820722</v>
+        <v>0.29819297918213544</v>
       </c>
     </row>
     <row r="7">
@@ -3058,7 +3058,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="45">
-        <v>0.30962344130812669</v>
+        <v>0.30772090155759852</v>
       </c>
     </row>
     <row r="8">
@@ -3066,7 +3066,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="46">
-        <v>0.34103228160374255</v>
+        <v>0.3389239354351265</v>
       </c>
     </row>
     <row r="9">
@@ -3074,7 +3074,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="47">
-        <v>0.34534864004947086</v>
+        <v>0.34197893967478338</v>
       </c>
     </row>
     <row r="10">
@@ -3082,7 +3082,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="48">
-        <v>0.35756981483407368</v>
+        <v>0.35567291696210329</v>
       </c>
     </row>
     <row r="11">
@@ -3090,7 +3090,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="49">
-        <v>0.3459261687849659</v>
+        <v>0.34477695180900647</v>
       </c>
     </row>
     <row r="12">
@@ -3098,7 +3098,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="50">
-        <v>0.36507763554219708</v>
+        <v>0.36407374955133753</v>
       </c>
     </row>
     <row r="13">
@@ -3106,7 +3106,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="51">
-        <v>0.36135985280580751</v>
+        <v>0.36048395101588482</v>
       </c>
     </row>
     <row r="14">
@@ -3114,7 +3114,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="52">
-        <v>0.34176403584051313</v>
+        <v>0.34072801014514448</v>
       </c>
     </row>
   </sheetData>
@@ -3139,7 +3139,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="66">
-        <v>0.38962375068920796</v>
+        <v>0.38857699861986872</v>
       </c>
     </row>
     <row r="3">
@@ -3147,7 +3147,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="67">
-        <v>0.35013272522678474</v>
+        <v>0.35013216813164633</v>
       </c>
     </row>
     <row r="4">
@@ -3155,7 +3155,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="68">
-        <v>0.33560105848045369</v>
+        <v>0.33454413771583758</v>
       </c>
     </row>
     <row r="5">
@@ -3163,7 +3163,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="69">
-        <v>0.33786000628233709</v>
+        <v>0.33709995630745027</v>
       </c>
     </row>
     <row r="6">
@@ -3171,7 +3171,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="70">
-        <v>0.34992284445813565</v>
+        <v>0.34911389020118194</v>
       </c>
     </row>
     <row r="7">
@@ -3179,7 +3179,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="71">
-        <v>0.36987246153916636</v>
+        <v>0.36986970971027416</v>
       </c>
     </row>
     <row r="8">
@@ -3187,7 +3187,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="72">
-        <v>0.37918879405493178</v>
+        <v>0.3783673579948173</v>
       </c>
     </row>
     <row r="9">
@@ -3195,7 +3195,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="73">
-        <v>0.39730430782523829</v>
+        <v>0.39509736667288176</v>
       </c>
     </row>
     <row r="10">
@@ -3203,7 +3203,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="74">
-        <v>0.43327901300711374</v>
+        <v>0.43230166126136982</v>
       </c>
     </row>
     <row r="11">
@@ -3211,7 +3211,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="75">
-        <v>0.37716554138880465</v>
+        <v>0.37694890960802779</v>
       </c>
     </row>
     <row r="12">
@@ -3219,7 +3219,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="76">
-        <v>0.40284451908645863</v>
+        <v>0.40040152919292965</v>
       </c>
     </row>
     <row r="13">
@@ -3227,7 +3227,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="77">
-        <v>0.38363018719141767</v>
+        <v>0.38262475192506151</v>
       </c>
     </row>
     <row r="14">
@@ -3235,7 +3235,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="78">
-        <v>0.40009690277687021</v>
+        <v>0.39934057916015847</v>
       </c>
     </row>
   </sheetData>
@@ -3260,7 +3260,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="92">
-        <v>0.095728663831961255</v>
+        <v>0.094770990177251324</v>
       </c>
     </row>
     <row r="3">
@@ -3268,7 +3268,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="93">
-        <v>0.098645060617974872</v>
+        <v>0.097547650796243196</v>
       </c>
     </row>
     <row r="4">
@@ -3276,7 +3276,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="94">
-        <v>0.11816233935148186</v>
+        <v>0.11616432888001586</v>
       </c>
     </row>
     <row r="5">
@@ -3284,7 +3284,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="95">
-        <v>0.1109974983646137</v>
+        <v>0.11056445908463354</v>
       </c>
     </row>
     <row r="6">
@@ -3292,7 +3292,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="96">
-        <v>0.1210225337443173</v>
+        <v>0.11989382431214379</v>
       </c>
     </row>
     <row r="7">
@@ -3300,7 +3300,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="97">
-        <v>0.11628320978493514</v>
+        <v>0.11524982252360545</v>
       </c>
     </row>
     <row r="8">
@@ -3308,7 +3308,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="98">
-        <v>0.13186828762801642</v>
+        <v>0.13020432931489517</v>
       </c>
     </row>
     <row r="9">
@@ -3316,7 +3316,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="99">
-        <v>0.12632517686286124</v>
+        <v>0.12490895838313447</v>
       </c>
     </row>
     <row r="10">
@@ -3324,7 +3324,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="100">
-        <v>0.14785106266691245</v>
+        <v>0.14632465328244704</v>
       </c>
     </row>
     <row r="11">
@@ -3332,7 +3332,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="101">
-        <v>0.14716653226137483</v>
+        <v>0.14590848236839446</v>
       </c>
     </row>
     <row r="12">
@@ -3340,7 +3340,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="102">
-        <v>0.16820928283299844</v>
+        <v>0.16720606442364083</v>
       </c>
     </row>
     <row r="13">
@@ -3348,7 +3348,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="103">
-        <v>0.1828905513938231</v>
+        <v>0.18195233636606714</v>
       </c>
     </row>
     <row r="14">
@@ -3356,7 +3356,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="104">
-        <v>0.18155992910849636</v>
+        <v>0.18063588838612177</v>
       </c>
     </row>
   </sheetData>
@@ -3389,7 +3389,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="119">
-        <v>0.37548236017236192</v>
+        <v>0.3754839854647451</v>
       </c>
     </row>
     <row r="4">
@@ -3405,7 +3405,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="121">
-        <v>0.37423611703488868</v>
+        <v>0.37423568791499756</v>
       </c>
     </row>
     <row r="6">
@@ -3413,7 +3413,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="122">
-        <v>0.34561082966531021</v>
+        <v>0.34507238201236479</v>
       </c>
     </row>
     <row r="7">
@@ -3453,7 +3453,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="127">
-        <v>0.39337611884694196</v>
+        <v>0.39337722018769694</v>
       </c>
     </row>
     <row r="12">
@@ -3461,7 +3461,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="128">
-        <v>0.40274989568818248</v>
+        <v>0.4005924929894365</v>
       </c>
     </row>
     <row r="13">
@@ -3469,7 +3469,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="129">
-        <v>0.43938963650550872</v>
+        <v>0.43938988240130689</v>
       </c>
     </row>
     <row r="14">
@@ -3477,7 +3477,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="130">
-        <v>0.42359669411698903</v>
+        <v>0.42359808779306579</v>
       </c>
     </row>
   </sheetData>
@@ -3502,7 +3502,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="144">
-        <v>0.37128061769720033</v>
+        <v>0.37109431634858131</v>
       </c>
     </row>
     <row r="3">
@@ -3510,7 +3510,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="145">
-        <v>0.36442153016148549</v>
+        <v>0.36364046890162621</v>
       </c>
     </row>
     <row r="4">
@@ -3518,7 +3518,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="146">
-        <v>0.36039842755948876</v>
+        <v>0.36015223395100943</v>
       </c>
     </row>
     <row r="5">
@@ -3526,7 +3526,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="147">
-        <v>0.37761709951018685</v>
+        <v>0.37551720837682817</v>
       </c>
     </row>
     <row r="6">
@@ -3534,7 +3534,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="148">
-        <v>0.3970097001518586</v>
+        <v>0.3933353352122278</v>
       </c>
     </row>
     <row r="7">
@@ -3542,7 +3542,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="149">
-        <v>0.3934813744304208</v>
+        <v>0.39038376742140696</v>
       </c>
     </row>
     <row r="8">
@@ -3550,7 +3550,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="150">
-        <v>0.38768629205780703</v>
+        <v>0.38642033829911249</v>
       </c>
     </row>
     <row r="9">
@@ -3558,7 +3558,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="151">
-        <v>0.39477430961820481</v>
+        <v>0.39140160227489568</v>
       </c>
     </row>
     <row r="10">
@@ -3566,7 +3566,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="152">
-        <v>0.4066174556617036</v>
+        <v>0.40459308795313659</v>
       </c>
     </row>
     <row r="11">
@@ -3574,7 +3574,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="153">
-        <v>0.43214009628130889</v>
+        <v>0.43037099477861473</v>
       </c>
     </row>
     <row r="12">
@@ -3582,7 +3582,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="154">
-        <v>0.41105517222079802</v>
+        <v>0.4094987783226986</v>
       </c>
     </row>
     <row r="13">
@@ -3590,7 +3590,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="155">
-        <v>0.41226942125206839</v>
+        <v>0.41184490321533923</v>
       </c>
     </row>
     <row r="14">
@@ -3598,7 +3598,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="156">
-        <v>0.43283726563221053</v>
+        <v>0.43180056654800986</v>
       </c>
     </row>
   </sheetData>
@@ -3623,7 +3623,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="170">
-        <v>0.48986290201393901</v>
+        <v>0.48851894573047899</v>
       </c>
     </row>
     <row r="3">
@@ -3631,7 +3631,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="171">
-        <v>0.44532833066042171</v>
+        <v>0.4453275835308742</v>
       </c>
     </row>
     <row r="4">
@@ -3639,7 +3639,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="172">
-        <v>0.44512301368532603</v>
+        <v>0.44417413733880856</v>
       </c>
     </row>
     <row r="5">
@@ -3647,7 +3647,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="173">
-        <v>0.45315301192522062</v>
+        <v>0.45315221449450466</v>
       </c>
     </row>
     <row r="6">
@@ -3655,7 +3655,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="174">
-        <v>0.46792906947607465</v>
+        <v>0.46763231946796613</v>
       </c>
     </row>
     <row r="7">
@@ -3663,7 +3663,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="175">
-        <v>0.46551927830691076</v>
+        <v>0.46379583464288921</v>
       </c>
     </row>
     <row r="8">
@@ -3671,7 +3671,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="176">
-        <v>0.48486551124294625</v>
+        <v>0.48399485430476752</v>
       </c>
     </row>
     <row r="9">
@@ -3679,7 +3679,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="177">
-        <v>0.49875991936160124</v>
+        <v>0.49876002605517578</v>
       </c>
     </row>
     <row r="10">
@@ -3687,7 +3687,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="178">
-        <v>0.50195896912354132</v>
+        <v>0.50070210803452719</v>
       </c>
     </row>
     <row r="11">
@@ -3695,7 +3695,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="179">
-        <v>0.51555392537978817</v>
+        <v>0.51500278699195867</v>
       </c>
     </row>
     <row r="12">
@@ -3703,7 +3703,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="180">
-        <v>0.5344167366584669</v>
+        <v>0.53418129295083849</v>
       </c>
     </row>
     <row r="13">
@@ -3711,7 +3711,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="181">
-        <v>0.55859180449157153</v>
+        <v>0.55847712033100949</v>
       </c>
     </row>
     <row r="14">
@@ -3719,7 +3719,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="182">
-        <v>0.57332346226152153</v>
+        <v>0.57344235600009574</v>
       </c>
     </row>
   </sheetData>
